--- a/building_inspector_forms/001_unit_inspection_form--building_inspector_forms.xlsx
+++ b/building_inspector_forms/001_unit_inspection_form--building_inspector_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1381,17 +1381,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>appliance_status_choices</t>
+          <t>electrical_outlets_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>working</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dishwasher</t>
+          <t>Working</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>not_working</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Working</t>
+          <t>Not Working</t>
         </is>
       </c>
     </row>
@@ -1420,29 +1420,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_working</t>
+          <t>broken</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Not Working</t>
+          <t>Broken</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>electrical_outlets_choices</t>
+          <t>plumbing_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>broken</t>
+          <t>working</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Broken</t>
+          <t>Working</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>not_working</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Working</t>
+          <t>Not Working</t>
         </is>
       </c>
     </row>
@@ -1471,29 +1471,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>not_working</t>
+          <t>broken</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Not Working</t>
+          <t>Broken</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>plumbing_choices</t>
+          <t>heating_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>broken</t>
+          <t>working</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Broken</t>
+          <t>Working</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>not_working</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Working</t>
+          <t>Not Working</t>
         </is>
       </c>
     </row>
@@ -1522,29 +1522,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>not_working</t>
+          <t>broken</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Not Working</t>
+          <t>Broken</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>heating_choices</t>
+          <t>air_conditioning_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>broken</t>
+          <t>working</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Broken</t>
+          <t>Working</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>not_working</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Working</t>
+          <t>Not Working</t>
         </is>
       </c>
     </row>
@@ -1573,29 +1573,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>not_working</t>
+          <t>broken</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Not Working</t>
+          <t>Broken</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>air_conditioning_choices</t>
+          <t>smoke_detectors_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>broken</t>
+          <t>working</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Broken</t>
+          <t>Working</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>not_working</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Working</t>
+          <t>Not Working</t>
         </is>
       </c>
     </row>
@@ -1624,29 +1624,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>not_working</t>
+          <t>broken</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Not Working</t>
+          <t>Broken</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>smoke_detectors_choices</t>
+          <t>fire_extinguishers_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>broken</t>
+          <t>present</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Broken</t>
+          <t>Present</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>not_present</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Present</t>
+          <t>Not Present</t>
         </is>
       </c>
     </row>
@@ -1675,29 +1675,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>not_present</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Not Present</t>
+          <t>Not Required</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>fire_extinguishers_choices</t>
+          <t>fire_alarm_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>not_required</t>
+          <t>working</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Not Required</t>
+          <t>Working</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>not_working</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Working</t>
+          <t>Not Working</t>
         </is>
       </c>
     </row>
@@ -1726,29 +1726,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>not_working</t>
+          <t>broken</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Not Working</t>
+          <t>Broken</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>fire_alarm_choices</t>
+          <t>sprinkler_system_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>broken</t>
+          <t>present</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Broken</t>
+          <t>Present</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>not_present</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Present</t>
+          <t>Not Present</t>
         </is>
       </c>
     </row>
@@ -1777,29 +1777,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>not_present</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Not Present</t>
+          <t>Not Required</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>sprinkler_system_choices</t>
+          <t>emergency_exits_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>not_required</t>
+          <t>working</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Not Required</t>
+          <t>Working</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>working</t>
+          <t>not_working</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Working</t>
+          <t>Not Working</t>
         </is>
       </c>
     </row>
@@ -1828,29 +1828,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>not_working</t>
+          <t>broken</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Not Working</t>
+          <t>Broken</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>emergency_exits_choices</t>
+          <t>fire_extinguisher_location_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>broken</t>
+          <t>present</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Broken</t>
+          <t>Present</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>not_present</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Present</t>
+          <t>Not Present</t>
         </is>
       </c>
     </row>
@@ -1879,29 +1879,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>not_present</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Not Present</t>
+          <t>Not Required</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>fire_extinguisher_location_choices</t>
+          <t>fire_alarm_location_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>not_required</t>
+          <t>present</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Not Required</t>
+          <t>Present</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>not_present</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Present</t>
+          <t>Not Present</t>
         </is>
       </c>
     </row>
@@ -1930,29 +1930,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>not_present</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Not Present</t>
+          <t>Not Required</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>fire_alarm_location_choices</t>
+          <t>smoke_detector_location_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>not_required</t>
+          <t>present</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Not Required</t>
+          <t>Present</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>not_present</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Present</t>
+          <t>Not Present</t>
         </is>
       </c>
     </row>
@@ -1981,29 +1981,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>not_present</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Not Present</t>
+          <t>Not Required</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>smoke_detector_location_choices</t>
+          <t>safety_equipment_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>not_required</t>
+          <t>present</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Not Required</t>
+          <t>Present</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>not_present</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Present</t>
+          <t>Not Present</t>
         </is>
       </c>
     </row>
@@ -2032,29 +2032,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>not_present</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Not Present</t>
+          <t>Not Required</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>safety_equipment_choices</t>
+          <t>fire_escape_route_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>not_required</t>
+          <t>present</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Not Required</t>
+          <t>Present</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>not_present</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Present</t>
+          <t>Not Present</t>
         </is>
       </c>
     </row>
@@ -2083,27 +2083,10 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>not_present</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
-        <is>
-          <t>Not Present</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>fire_escape_route_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>not_required</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
         <is>
           <t>Not Required</t>
         </is>
